--- a/Docs/X-7 기지 기획서/X-7 수치 종합표.xlsx
+++ b/Docs/X-7 기지 기획서/X-7 수치 종합표.xlsx
@@ -20,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;₡&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="+#,##0&quot;₡&quot;;-#,##0&quot;₡&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -133,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -207,9 +206,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3579,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3844,22 +3840,20 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-03a</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>퀘스트 실패·파괴 위약</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>보수 예정액의 40%</t>
-        </is>
+          <t>붕괴 과태료(무지지)</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>-250</v>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>대상 파괴/실패 시</t>
+          <t>붕괴 시</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -3871,16 +3865,16 @@
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>M-03a</t>
+          <t>M-03b</t>
         </is>
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>붕괴 과태료(무지지)</t>
+          <t>붕괴 과태료(지지있음)</t>
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>-250</v>
+        <v>-150</v>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
@@ -3896,97 +3890,99 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>M-03b</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>붕괴 과태료(지지있음)</t>
+          <t>미복귀 과태료</t>
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>-150</v>
+        <v>-40</v>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>붕괴 시</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>인당</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>미복귀 과태료</t>
+          <t>사망 처리비</t>
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>부활</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>인당</t>
+          <t>회당</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>사망 처리비</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="n">
-        <v>-30</v>
+          <t>경고 착수금 삭감</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>다음날 착수금 ×0.7</t>
+        </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>부활</t>
+          <t>Day2/3 실패 후</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>회당</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>경고 착수금 삭감</t>
+          <t>대출 이자</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>다음날 착수금 ×0.7</t>
+          <t>원금 × 일 이자율(5%)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>Day2/3 실패 후</t>
+          <t>일 정산</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -3998,22 +3994,22 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>대출 이자</t>
+          <t>대출 상환</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>원금 × 일 이자율(5%)</t>
+          <t>임의/정산</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>일 정산</t>
+          <t>상인</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -4025,52 +4021,32 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>대출 상환</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>임의/정산</t>
-        </is>
+          <t>부상 치료비</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>-70</v>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>상인</t>
+          <t>모선에서 상인에게 지불 시</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>부상→건강 유일한 회복 수단, 아이템 아님 (07 §2.5)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>M-09</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>부상 치료비</t>
-        </is>
-      </c>
-      <c r="C24" s="25" t="n">
-        <v>-70</v>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>모선에서 상인에게 지불 시</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>부상→건강 유일한 회복 수단, 아이템 아님 (07 §2.5)</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>삭제(M-02): 퀘스트 실패·파괴 위약금. 퀘스트 실패는 크레딧 손실 없이 호감도만 하락한다.</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4420,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>실패·파괴 위약(₡)</t>
+          <t>실패 시</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4467,9 +4443,10 @@
       <c r="C51" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="D51" s="27">
-        <f>-ROUND(C51*0.4,0)</f>
-        <v/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>크레딧 0 (호감도만 하락)</t>
+        </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
@@ -4491,9 +4468,10 @@
       <c r="C52" s="14" t="n">
         <v>160</v>
       </c>
-      <c r="D52" s="27">
-        <f>-ROUND(C52*0.4,0)</f>
-        <v/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>크레딧 0 (호감도만 하락)</t>
+        </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -4515,9 +4493,10 @@
       <c r="C53" s="14" t="n">
         <v>280</v>
       </c>
-      <c r="D53" s="27">
-        <f>-ROUND(C53*0.4,0)</f>
-        <v/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>크레딧 0 (호감도만 하락)</t>
+        </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
@@ -4539,9 +4518,10 @@
       <c r="C54" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="D54" s="27">
-        <f>-ROUND(C54*0.4,0)</f>
-        <v/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>크레딧 0 (호감도만 하락)</t>
+        </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -4563,9 +4543,10 @@
       <c r="C55" s="14" t="n">
         <v>350</v>
       </c>
-      <c r="D55" s="27">
-        <f>-ROUND(C55*0.4,0)</f>
-        <v/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>크레딧 0 (호감도만 하락)</t>
+        </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -4591,7 +4572,7 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>미회수·파괴 시 위약 동일</t>
+          <t>크레딧 0 (호감도만 하락)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4616,12 +4597,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>크레딧 0 (호감도만 하락)</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>미달 시 0 (위약 없음)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4641,50 +4622,42 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>크레딧 0 (호감도만 하락)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>미달 시 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>실패(미회수·파괴·포기) 시 크레딧 위약금 없음 — 팀 결정. 호감도만 하락(미회수&lt;파괴), 정확한 델타값은 미확정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>대출</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="9" t="n"/>
-      <c r="E60" s="9" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>대출 가능처</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>모선 상인만</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>기본 한도</t>
+          <t>대출 가능처</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>800₡</t>
+          <t>모선 상인만</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -4694,12 +4667,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>호감 ≥+2 한도</t>
+          <t>기본 한도</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>1,200₡</t>
+          <t>800₡</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -4709,12 +4682,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>호감 ≤-2 한도</t>
+          <t>호감 ≥+2 한도</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>400₡</t>
+          <t>1,200₡</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -4724,12 +4697,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>일 이자</t>
+          <t>호감 ≤-2 한도</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>5% (미상환 잔액)</t>
+          <t>400₡</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -4739,160 +4712,177 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>패널티</t>
+          <t>일 이자</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>이자만 (입장 금지·강제 호감↓ 없음)</t>
+          <t>5% (미상환 잔액)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr"/>
     </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>패널티</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>이자만 (입장 금지·강제 호감↓ 없음)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>난이도별 상점·물가 배율</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="9" t="n"/>
-      <c r="E68" s="9" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>난이도</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>착수(₡)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>소모품 물가</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>장비 물가</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>환급 / 과태료</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>안전</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="n">
-        <v>700</v>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>×0.85</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>×0.9</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>×1.0 / ×0.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>표준</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="B71" s="14" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>×1.0</t>
+          <t>×0.85</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>×1.0</t>
+          <t>×0.9</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>×1.0 / ×1.0</t>
+          <t>×1.0 / ×0.8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>위험</t>
+          <t>표준</t>
         </is>
       </c>
       <c r="B72" s="14" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>×1.15</t>
+          <t>×1.0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>×1.1</t>
+          <t>×1.0</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>×1.1 / ×1.2</t>
+          <t>×1.0 / ×1.0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>위험</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>×1.15</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>×1.1</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>×1.1 / ×1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
           <t>극한</t>
         </is>
       </c>
-      <c r="B73" s="14" t="n">
+      <c r="B74" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>×1.25</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>×1.2</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>×1.2 / ×1.4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
